--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC94F40E-385A-4C17-98E4-8CFD8080ABDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B4903D-55ED-4A94-9CB3-3303B73EE87D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="372">
   <si>
     <t>id</t>
   </si>
@@ -1150,6 +1150,21 @@
   </si>
   <si>
     <t xml:space="preserve">30 Images featuring famous robots, androids and synthetic characters from films, TV and sci‑fi. </t>
+  </si>
+  <si>
+    <t>Q0075</t>
+  </si>
+  <si>
+    <t>RH-GK075</t>
+  </si>
+  <si>
+    <t>quizzes/Airports_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>Airports</t>
+  </si>
+  <si>
+    <t>25/75 Images. The picture is split into three sections. In each section, identify (1) the cartoon character, (2) the celebrity, and (3) the brand/logo. Take the first letter of each correct answer—this gives you a three‑letter airport code for a capital city. From that airport code, write down the country that the capital city belongs to.</t>
   </si>
 </sst>
 </file>
@@ -1590,7 +1605,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr defaultColWidth="23.28515625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="5" width="23.28515625" style="1"/>
@@ -3098,6 +3113,26 @@
         <v>364</v>
       </c>
     </row>
+    <row r="76" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="E76" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="F76" s="7" t="s">
+        <v>369</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B4903D-55ED-4A94-9CB3-3303B73EE87D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44B71803-06D6-49B6-9850-CD5F6BE3547E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="377">
   <si>
     <t>id</t>
   </si>
@@ -1165,6 +1165,21 @@
   </si>
   <si>
     <t>25/75 Images. The picture is split into three sections. In each section, identify (1) the cartoon character, (2) the celebrity, and (3) the brand/logo. Take the first letter of each correct answer—this gives you a three‑letter airport code for a capital city. From that airport code, write down the country that the capital city belongs to.</t>
+  </si>
+  <si>
+    <t>Q0076</t>
+  </si>
+  <si>
+    <t>RH-GK076</t>
+  </si>
+  <si>
+    <t>30 Images. Mostly of personalities named Dave or David.</t>
+  </si>
+  <si>
+    <t>Mostly Daves</t>
+  </si>
+  <si>
+    <t>quizzes/Mostly_Daves_Quiz.pdf</t>
   </si>
 </sst>
 </file>
@@ -1605,7 +1620,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F76"/>
+  <dimension ref="A1:F77"/>
   <sheetFormatPr defaultColWidth="23.28515625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="5" width="23.28515625" style="1"/>
@@ -3133,6 +3148,26 @@
         <v>369</v>
       </c>
     </row>
+    <row r="77" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="E77" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="F77" s="7" t="s">
+        <v>376</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44B71803-06D6-49B6-9850-CD5F6BE3547E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC138D59-3421-4FF0-8562-636C7E4093BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15540" yWindow="-16320" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quizzes" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="382">
   <si>
     <t>id</t>
   </si>
@@ -1180,6 +1180,21 @@
   </si>
   <si>
     <t>quizzes/Mostly_Daves_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>Q0077</t>
+  </si>
+  <si>
+    <t>RH-GK077</t>
+  </si>
+  <si>
+    <t>30 Images. They’re all Toms, Tommys or Thomases — you just need to name the surname.</t>
+  </si>
+  <si>
+    <t>quizzes/Toms_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>Toms</t>
   </si>
 </sst>
 </file>
@@ -1620,7 +1635,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F77"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr defaultColWidth="23.28515625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="5" width="23.28515625" style="1"/>
@@ -3168,6 +3183,26 @@
         <v>376</v>
       </c>
     </row>
+    <row r="78" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="E78" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="F78" s="7" t="s">
+        <v>380</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC138D59-3421-4FF0-8562-636C7E4093BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3180EE0B-4799-4976-A0A4-92C5E2E50B3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15540" yWindow="-16320" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quizzes" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="387">
   <si>
     <t>id</t>
   </si>
@@ -1195,6 +1195,21 @@
   </si>
   <si>
     <t>Toms</t>
+  </si>
+  <si>
+    <t>Q0078</t>
+  </si>
+  <si>
+    <t>RH-GK078</t>
+  </si>
+  <si>
+    <t>(in)Famous Fiddlers</t>
+  </si>
+  <si>
+    <t>25 Images of (in)Famous Fiddlers.</t>
+  </si>
+  <si>
+    <t>quizzes/(in)Famous_Fiddlers_Quiz.pdf</t>
   </si>
 </sst>
 </file>
@@ -1635,7 +1650,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr defaultColWidth="23.28515625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="5" width="23.28515625" style="1"/>
@@ -3203,6 +3218,26 @@
         <v>380</v>
       </c>
     </row>
+    <row r="79" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="E79" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="F79" s="7" t="s">
+        <v>386</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3180EE0B-4799-4976-A0A4-92C5E2E50B3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23D20096-354A-4354-85F2-FA16DDE98B3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15540" yWindow="-16320" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quizzes" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="392">
   <si>
     <t>id</t>
   </si>
@@ -1210,6 +1210,21 @@
   </si>
   <si>
     <t>quizzes/(in)Famous_Fiddlers_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>Marks</t>
+  </si>
+  <si>
+    <t>28 Images. All pictures feature well‑known Marks, Marcs or Marcos.</t>
+  </si>
+  <si>
+    <t>quizzes/Marks_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>Q0079</t>
+  </si>
+  <si>
+    <t>RH-GK079</t>
   </si>
 </sst>
 </file>
@@ -1650,7 +1665,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr defaultColWidth="23.28515625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="5" width="23.28515625" style="1"/>
@@ -3223,18 +3238,38 @@
         <v>382</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>383</v>
       </c>
       <c r="D79" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E79" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="F79" s="7" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="D80" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="E79" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="F79" s="7" t="s">
+      <c r="E80" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="F80" s="7" t="s">
         <v>386</v>
       </c>
     </row>

--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23D20096-354A-4354-85F2-FA16DDE98B3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E0487F-8A2F-4206-91BE-7E09A1911803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15540" yWindow="-16320" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quizzes" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="397">
   <si>
     <t>id</t>
   </si>
@@ -1225,6 +1225,21 @@
   </si>
   <si>
     <t>RH-GK079</t>
+  </si>
+  <si>
+    <t>Q0080</t>
+  </si>
+  <si>
+    <t>Alans</t>
+  </si>
+  <si>
+    <t>28 Images. Every picture shows a famous Alan or Allen. Just name the person.</t>
+  </si>
+  <si>
+    <t>quizzes/Alans_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>RH-GK080</t>
   </si>
 </sst>
 </file>
@@ -1665,7 +1680,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr defaultColWidth="23.28515625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="5" width="23.28515625" style="1"/>
@@ -3258,18 +3273,38 @@
         <v>390</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>391</v>
       </c>
       <c r="D80" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="E80" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="F80" s="7" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="D81" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="E80" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="F80" s="7" t="s">
+      <c r="E81" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="F81" s="7" t="s">
         <v>386</v>
       </c>
     </row>

--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E0487F-8A2F-4206-91BE-7E09A1911803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DA6318F-769A-4F6B-8340-2BDEA7C0A5FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15540" yWindow="-16320" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quizzes" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="407">
   <si>
     <t>id</t>
   </si>
@@ -1240,6 +1240,36 @@
   </si>
   <si>
     <t>RH-GK080</t>
+  </si>
+  <si>
+    <t>Bills</t>
+  </si>
+  <si>
+    <t>Wills</t>
+  </si>
+  <si>
+    <t>quizzes/Bills_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>quizzes/Wills_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>Q0081</t>
+  </si>
+  <si>
+    <t>Q0082</t>
+  </si>
+  <si>
+    <t>RH-GK081</t>
+  </si>
+  <si>
+    <t>RH-GK082</t>
+  </si>
+  <si>
+    <t>30 Images. This round is packed with Bills — identify each one by giving their full name.</t>
+  </si>
+  <si>
+    <t>30 Images. This round is packed with Wills — identify each one by giving their full name.</t>
   </si>
 </sst>
 </file>
@@ -1680,7 +1710,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr defaultColWidth="23.28515625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="5" width="23.28515625" style="1"/>
@@ -3293,18 +3323,58 @@
         <v>392</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>396</v>
       </c>
       <c r="D81" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="E81" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="F81" s="7" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="E82" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="F82" s="7" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="D83" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="E81" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="F81" s="7" t="s">
+      <c r="E83" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="F83" s="7" t="s">
         <v>386</v>
       </c>
     </row>

--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DA6318F-769A-4F6B-8340-2BDEA7C0A5FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{974DF682-E3CF-49C3-A4BB-84FC26147B63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15540" yWindow="-16320" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quizzes" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="417">
   <si>
     <t>id</t>
   </si>
@@ -1270,6 +1270,36 @@
   </si>
   <si>
     <t>30 Images. This round is packed with Wills — identify each one by giving their full name.</t>
+  </si>
+  <si>
+    <t>quizzes/Dans_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>Dans</t>
+  </si>
+  <si>
+    <t>Q0083</t>
+  </si>
+  <si>
+    <t>RH-GK083</t>
+  </si>
+  <si>
+    <t>30 Images. All these people share a variation of ‘Dan/Danny/Daniels’ in their name — identify each one.</t>
+  </si>
+  <si>
+    <t>30 Images. All these people share a variation of ‘Sam’ in their name — identify each one.</t>
+  </si>
+  <si>
+    <t>Sams</t>
+  </si>
+  <si>
+    <t>quizzes/Sams_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>Q0084</t>
+  </si>
+  <si>
+    <t>RH-GK084</t>
   </si>
 </sst>
 </file>
@@ -1310,7 +1340,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1347,6 +1377,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1375,7 +1411,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1407,6 +1443,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1710,7 +1755,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr defaultColWidth="23.28515625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="5" width="23.28515625" style="1"/>
@@ -2299,122 +2344,122 @@
       </c>
     </row>
     <row r="30" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="E30" s="12" t="s">
-        <v>314</v>
-      </c>
-      <c r="F30" s="4" t="s">
+      <c r="E30" s="21" t="s">
+        <v>314</v>
+      </c>
+      <c r="F30" s="20" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="E31" s="12" t="s">
-        <v>314</v>
-      </c>
-      <c r="F31" s="4" t="s">
+      <c r="E31" s="21" t="s">
+        <v>314</v>
+      </c>
+      <c r="F31" s="20" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="E32" s="12" t="s">
-        <v>314</v>
-      </c>
-      <c r="F32" s="4" t="s">
+      <c r="E32" s="21" t="s">
+        <v>314</v>
+      </c>
+      <c r="F32" s="20" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="20" t="s">
         <v>208</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="E33" s="12" t="s">
-        <v>314</v>
-      </c>
-      <c r="F33" s="4" t="s">
+      <c r="E33" s="21" t="s">
+        <v>314</v>
+      </c>
+      <c r="F33" s="20" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="19" t="s">
         <v>154</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B34" s="20" t="s">
         <v>209</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="D34" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="E34" s="12" t="s">
-        <v>314</v>
-      </c>
-      <c r="F34" s="4" t="s">
+      <c r="E34" s="21" t="s">
+        <v>314</v>
+      </c>
+      <c r="F34" s="20" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="E35" s="12" t="s">
-        <v>314</v>
-      </c>
-      <c r="F35" s="4" t="s">
+      <c r="E35" s="21" t="s">
+        <v>314</v>
+      </c>
+      <c r="F35" s="20" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3259,122 +3304,162 @@
       </c>
     </row>
     <row r="78" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="6" t="s">
+      <c r="A78" s="17" t="s">
         <v>377</v>
       </c>
-      <c r="B78" s="7" t="s">
+      <c r="B78" s="8" t="s">
         <v>381</v>
       </c>
-      <c r="C78" s="6" t="s">
+      <c r="C78" s="17" t="s">
         <v>378</v>
       </c>
-      <c r="D78" s="7" t="s">
+      <c r="D78" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="E78" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="F78" s="7" t="s">
+      <c r="E78" s="18" t="s">
+        <v>314</v>
+      </c>
+      <c r="F78" s="8" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="6" t="s">
+      <c r="A79" s="17" t="s">
         <v>382</v>
       </c>
-      <c r="B79" s="7" t="s">
+      <c r="B79" s="8" t="s">
         <v>387</v>
       </c>
-      <c r="C79" s="6" t="s">
+      <c r="C79" s="17" t="s">
         <v>383</v>
       </c>
-      <c r="D79" s="7" t="s">
+      <c r="D79" s="8" t="s">
         <v>388</v>
       </c>
-      <c r="E79" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="F79" s="7" t="s">
+      <c r="E79" s="18" t="s">
+        <v>314</v>
+      </c>
+      <c r="F79" s="8" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="6" t="s">
+      <c r="A80" s="17" t="s">
         <v>390</v>
       </c>
-      <c r="B80" s="7" t="s">
+      <c r="B80" s="8" t="s">
         <v>393</v>
       </c>
-      <c r="C80" s="6" t="s">
+      <c r="C80" s="17" t="s">
         <v>391</v>
       </c>
-      <c r="D80" s="7" t="s">
+      <c r="D80" s="8" t="s">
         <v>394</v>
       </c>
-      <c r="E80" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="F80" s="7" t="s">
+      <c r="E80" s="18" t="s">
+        <v>314</v>
+      </c>
+      <c r="F80" s="8" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="6" t="s">
+      <c r="A81" s="17" t="s">
         <v>392</v>
       </c>
-      <c r="B81" s="7" t="s">
+      <c r="B81" s="8" t="s">
         <v>397</v>
       </c>
-      <c r="C81" s="6" t="s">
+      <c r="C81" s="17" t="s">
         <v>396</v>
       </c>
-      <c r="D81" s="7" t="s">
+      <c r="D81" s="8" t="s">
         <v>405</v>
       </c>
-      <c r="E81" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="F81" s="7" t="s">
+      <c r="E81" s="18" t="s">
+        <v>314</v>
+      </c>
+      <c r="F81" s="8" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="6" t="s">
+      <c r="A82" s="17" t="s">
         <v>401</v>
       </c>
-      <c r="B82" s="7" t="s">
+      <c r="B82" s="8" t="s">
         <v>398</v>
       </c>
-      <c r="C82" s="6" t="s">
+      <c r="C82" s="17" t="s">
         <v>403</v>
       </c>
-      <c r="D82" s="7" t="s">
+      <c r="D82" s="8" t="s">
         <v>406</v>
       </c>
-      <c r="E82" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="F82" s="7" t="s">
+      <c r="E82" s="18" t="s">
+        <v>314</v>
+      </c>
+      <c r="F82" s="8" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="6" t="s">
+      <c r="A83" s="17" t="s">
         <v>402</v>
       </c>
-      <c r="B83" s="7" t="s">
+      <c r="B83" s="8" t="s">
+        <v>408</v>
+      </c>
+      <c r="C83" s="17" t="s">
+        <v>404</v>
+      </c>
+      <c r="D83" s="8" t="s">
+        <v>411</v>
+      </c>
+      <c r="E83" s="18" t="s">
+        <v>314</v>
+      </c>
+      <c r="F83" s="8" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="17" t="s">
+        <v>409</v>
+      </c>
+      <c r="B84" s="8" t="s">
+        <v>413</v>
+      </c>
+      <c r="C84" s="17" t="s">
+        <v>410</v>
+      </c>
+      <c r="D84" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="E84" s="18" t="s">
+        <v>314</v>
+      </c>
+      <c r="F84" s="8" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="B85" s="7" t="s">
         <v>384</v>
       </c>
-      <c r="C83" s="6" t="s">
-        <v>404</v>
-      </c>
-      <c r="D83" s="7" t="s">
+      <c r="C85" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="D85" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="E83" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="F83" s="7" t="s">
+      <c r="E85" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="F85" s="7" t="s">
         <v>386</v>
       </c>
     </row>

--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{974DF682-E3CF-49C3-A4BB-84FC26147B63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53CC3205-0558-476A-AF76-B557C97C66CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="437">
   <si>
     <t>id</t>
   </si>
@@ -1300,6 +1300,66 @@
   </si>
   <si>
     <t>RH-GK084</t>
+  </si>
+  <si>
+    <t>quizzes/Jameses_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>Jameses</t>
+  </si>
+  <si>
+    <t>RH-GK085</t>
+  </si>
+  <si>
+    <t>Q0085</t>
+  </si>
+  <si>
+    <t>30 Images. All these people share a ‘James’ in their name — identify each one.</t>
+  </si>
+  <si>
+    <t>Petes</t>
+  </si>
+  <si>
+    <t>30 Images. All these people share a ‘Pete’ in their name — identify each one.</t>
+  </si>
+  <si>
+    <t>quizzes/Petes_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>RH-GK086</t>
+  </si>
+  <si>
+    <t>Q0086</t>
+  </si>
+  <si>
+    <t>RH-GK087</t>
+  </si>
+  <si>
+    <t>Q0087</t>
+  </si>
+  <si>
+    <t>30 Images. All these people share a ‘Paul’ in their name — identify each one.</t>
+  </si>
+  <si>
+    <t>quizzes/Pauls_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>Pauls</t>
+  </si>
+  <si>
+    <t>30 Images. All these people share a ‘Ste’ in their name — identify each one.</t>
+  </si>
+  <si>
+    <t>Q0088</t>
+  </si>
+  <si>
+    <t>RH-GK088</t>
+  </si>
+  <si>
+    <t>Steves</t>
+  </si>
+  <si>
+    <t>quizzes/Steves_Quiz.pdf</t>
   </si>
 </sst>
 </file>
@@ -1755,7 +1815,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr defaultColWidth="23.28515625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="5" width="23.28515625" style="1"/>
@@ -3444,22 +3504,102 @@
       </c>
     </row>
     <row r="85" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="6" t="s">
+      <c r="A85" s="17" t="s">
         <v>415</v>
       </c>
-      <c r="B85" s="7" t="s">
+      <c r="B85" s="8" t="s">
+        <v>418</v>
+      </c>
+      <c r="C85" s="17" t="s">
+        <v>416</v>
+      </c>
+      <c r="D85" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="E85" s="18" t="s">
+        <v>314</v>
+      </c>
+      <c r="F85" s="8" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="B86" s="8" t="s">
+        <v>422</v>
+      </c>
+      <c r="C86" s="17" t="s">
+        <v>419</v>
+      </c>
+      <c r="D86" s="8" t="s">
+        <v>423</v>
+      </c>
+      <c r="E86" s="18" t="s">
+        <v>314</v>
+      </c>
+      <c r="F86" s="8" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="17" t="s">
+        <v>426</v>
+      </c>
+      <c r="B87" s="8" t="s">
+        <v>431</v>
+      </c>
+      <c r="C87" s="17" t="s">
+        <v>425</v>
+      </c>
+      <c r="D87" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="E87" s="18" t="s">
+        <v>314</v>
+      </c>
+      <c r="F87" s="8" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="17" t="s">
+        <v>428</v>
+      </c>
+      <c r="B88" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="C88" s="17" t="s">
+        <v>427</v>
+      </c>
+      <c r="D88" s="8" t="s">
+        <v>432</v>
+      </c>
+      <c r="E88" s="18" t="s">
+        <v>314</v>
+      </c>
+      <c r="F88" s="8" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="17" t="s">
+        <v>433</v>
+      </c>
+      <c r="B89" s="7" t="s">
         <v>384</v>
       </c>
-      <c r="C85" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="D85" s="7" t="s">
+      <c r="C89" s="17" t="s">
+        <v>434</v>
+      </c>
+      <c r="D89" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="E85" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="F85" s="7" t="s">
+      <c r="E89" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="F89" s="7" t="s">
         <v>386</v>
       </c>
     </row>

--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53CC3205-0558-476A-AF76-B557C97C66CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F00F31D4-FC47-4085-94F3-2659CB72396D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15540" yWindow="-16320" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quizzes" sheetId="1" r:id="rId1"/>

--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F00F31D4-FC47-4085-94F3-2659CB72396D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F359921-38FF-4CA1-B65D-BBB7B228C0E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15540" yWindow="-16320" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quizzes" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="442">
   <si>
     <t>id</t>
   </si>
@@ -1360,6 +1360,21 @@
   </si>
   <si>
     <t>quizzes/Steves_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>quizzes/Jos_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>Jos</t>
+  </si>
+  <si>
+    <t>RH-GK089</t>
+  </si>
+  <si>
+    <t>Q0089</t>
+  </si>
+  <si>
+    <t>30 Images. All these people share a ‘Jo’ in their name — identify each one.</t>
   </si>
 </sst>
 </file>
@@ -1815,7 +1830,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F89"/>
+  <dimension ref="A1:F90"/>
   <sheetFormatPr defaultColWidth="23.28515625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="5" width="23.28515625" style="1"/>
@@ -3587,19 +3602,39 @@
       <c r="A89" s="17" t="s">
         <v>433</v>
       </c>
-      <c r="B89" s="7" t="s">
-        <v>384</v>
+      <c r="B89" s="8" t="s">
+        <v>438</v>
       </c>
       <c r="C89" s="17" t="s">
         <v>434</v>
       </c>
-      <c r="D89" s="7" t="s">
+      <c r="D89" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="E89" s="18" t="s">
+        <v>314</v>
+      </c>
+      <c r="F89" s="8" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="17" t="s">
+        <v>440</v>
+      </c>
+      <c r="B90" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="C90" s="17" t="s">
+        <v>439</v>
+      </c>
+      <c r="D90" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="E89" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="F89" s="7" t="s">
+      <c r="E90" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="F90" s="7" t="s">
         <v>386</v>
       </c>
     </row>

--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F359921-38FF-4CA1-B65D-BBB7B228C0E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E5C4DF-E2FB-4B97-A076-4DB7CBAFC804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-22860" yWindow="-16335" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quizzes" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="447">
   <si>
     <t>id</t>
   </si>
@@ -1375,6 +1375,21 @@
   </si>
   <si>
     <t>30 Images. All these people share a ‘Jo’ in their name — identify each one.</t>
+  </si>
+  <si>
+    <t>Q0090</t>
+  </si>
+  <si>
+    <t>quizzes/Disney_Pairs_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>Disney Pairs</t>
+  </si>
+  <si>
+    <t>RH-GK090</t>
+  </si>
+  <si>
+    <t>25 Images. Name the Character and Voice Artist.</t>
   </si>
 </sst>
 </file>
@@ -1486,7 +1501,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1527,6 +1542,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1830,7 +1846,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F90"/>
+  <dimension ref="A1:F91"/>
   <sheetFormatPr defaultColWidth="23.28515625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="5" width="23.28515625" style="1"/>
@@ -3638,6 +3654,26 @@
         <v>386</v>
       </c>
     </row>
+    <row r="91" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="19" t="s">
+        <v>442</v>
+      </c>
+      <c r="B91" s="22" t="s">
+        <v>444</v>
+      </c>
+      <c r="C91" s="19" t="s">
+        <v>445</v>
+      </c>
+      <c r="D91" s="20" t="s">
+        <v>446</v>
+      </c>
+      <c r="E91" s="21" t="s">
+        <v>314</v>
+      </c>
+      <c r="F91" s="20" t="s">
+        <v>443</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E5C4DF-E2FB-4B97-A076-4DB7CBAFC804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8221EDA-2238-4C40-A624-9207CE458CED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22860" yWindow="-16335" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quizzes" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="452">
   <si>
     <t>id</t>
   </si>
@@ -1390,6 +1390,21 @@
   </si>
   <si>
     <t>25 Images. Name the Character and Voice Artist.</t>
+  </si>
+  <si>
+    <t>Q0091</t>
+  </si>
+  <si>
+    <t>Andys</t>
+  </si>
+  <si>
+    <t>RH-GK091</t>
+  </si>
+  <si>
+    <t>quizzes/Andys_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>30 images. These famous faces all share a common link: a version of the name Andrew appears somewhere in their name.</t>
   </si>
 </sst>
 </file>
@@ -1846,7 +1861,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F91"/>
+  <dimension ref="A1:F92"/>
   <sheetFormatPr defaultColWidth="23.28515625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="5" width="23.28515625" style="1"/>
@@ -3674,6 +3689,26 @@
         <v>443</v>
       </c>
     </row>
+    <row r="92" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="17" t="s">
+        <v>447</v>
+      </c>
+      <c r="B92" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="C92" s="17" t="s">
+        <v>449</v>
+      </c>
+      <c r="D92" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="E92" s="18" t="s">
+        <v>314</v>
+      </c>
+      <c r="F92" s="8" t="s">
+        <v>450</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8221EDA-2238-4C40-A624-9207CE458CED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CEC5CFF-5203-485A-A8A4-B04DEDAE008F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="457">
   <si>
     <t>id</t>
   </si>
@@ -1404,7 +1404,22 @@
     <t>quizzes/Andys_Quiz.pdf</t>
   </si>
   <si>
-    <t>30 images. These famous faces all share a common link: a version of the name Andrew appears somewhere in their name.</t>
+    <t>quizzes/Rebus_TV_Shows_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>RH-GK092</t>
+  </si>
+  <si>
+    <t>Q0092</t>
+  </si>
+  <si>
+    <t>Rebus TV Shows</t>
+  </si>
+  <si>
+    <t>25 Images. Each picture is a rebus clue representing the title of a TV show. Can you work out the programme from the images?</t>
+  </si>
+  <si>
+    <t>30 Images. These famous faces all share a common link: a version of the name Andrew appears somewhere in their name.</t>
   </si>
 </sst>
 </file>
@@ -1861,7 +1876,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F92"/>
+  <dimension ref="A1:F93"/>
   <sheetFormatPr defaultColWidth="23.28515625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="5" width="23.28515625" style="1"/>
@@ -3700,13 +3715,33 @@
         <v>449</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="E92" s="18" t="s">
         <v>314</v>
       </c>
       <c r="F92" s="8" t="s">
         <v>450</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="17" t="s">
+        <v>453</v>
+      </c>
+      <c r="B93" s="8" t="s">
+        <v>454</v>
+      </c>
+      <c r="C93" s="17" t="s">
+        <v>452</v>
+      </c>
+      <c r="D93" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="E93" s="18" t="s">
+        <v>314</v>
+      </c>
+      <c r="F93" s="8" t="s">
+        <v>451</v>
       </c>
     </row>
   </sheetData>
